--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.457063115903294</v>
+        <v>0.3992727563342853</v>
       </c>
       <c r="D2" t="n">
-        <v>2.671880315292802</v>
+        <v>0.4341805512350803</v>
       </c>
       <c r="E2" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F2" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.45214229394428</v>
+        <v>9.660973122765947</v>
       </c>
       <c r="D3" t="n">
-        <v>59.04010308967546</v>
+        <v>9.594016752072262</v>
       </c>
       <c r="E3" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F3" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.11076672815155</v>
+        <v>6.517999593324627</v>
       </c>
       <c r="D4" t="n">
-        <v>39.67518669781118</v>
+        <v>6.447217838394317</v>
       </c>
       <c r="E4" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F4" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.17771388554036</v>
+        <v>8.316378506400309</v>
       </c>
       <c r="D5" t="n">
-        <v>50.74791427097934</v>
+        <v>8.246536069034143</v>
       </c>
       <c r="E5" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F5" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.88786544769679</v>
+        <v>7.781778135250729</v>
       </c>
       <c r="D6" t="n">
-        <v>46.33520820644092</v>
+        <v>7.529471333546651</v>
       </c>
       <c r="E6" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F6" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.57925775742428</v>
+        <v>4.319129385581445</v>
       </c>
       <c r="D7" t="n">
-        <v>25.50462580703269</v>
+        <v>4.144501693642812</v>
       </c>
       <c r="E7" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F7" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.41131878932013</v>
+        <v>6.404339303264522</v>
       </c>
       <c r="D8" t="n">
-        <v>38.2549631781602</v>
+        <v>6.216431516451033</v>
       </c>
       <c r="E8" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F8" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.85512457237081</v>
+        <v>2.088957743010257</v>
       </c>
       <c r="D9" t="n">
-        <v>14.60218831579942</v>
+        <v>2.372855601317406</v>
       </c>
       <c r="E9" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F9" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.74416884692422</v>
+        <v>4.670927437625187</v>
       </c>
       <c r="D10" t="n">
-        <v>53.58324377154482</v>
+        <v>8.707277112876033</v>
       </c>
       <c r="E10" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F10" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.39237648449654</v>
+        <v>2.988761178730688</v>
       </c>
       <c r="D11" t="n">
-        <v>35.05784255230542</v>
+        <v>5.696899414749631</v>
       </c>
       <c r="E11" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F11" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.76711524108125</v>
+        <v>6.299656226675704</v>
       </c>
       <c r="D12" t="n">
-        <v>38.98097506636375</v>
+        <v>6.334408448284109</v>
       </c>
       <c r="E12" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F12" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.13110095036568</v>
+        <v>7.821303904434423</v>
       </c>
       <c r="D13" t="n">
-        <v>48.32349242478806</v>
+        <v>7.852567519028059</v>
       </c>
       <c r="E13" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F13" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>33.01514803843835</v>
+        <v>5.364961556246233</v>
       </c>
       <c r="D14" t="n">
-        <v>58.14220019646186</v>
+        <v>9.448107531925054</v>
       </c>
       <c r="E14" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F14" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>43.48850422812907</v>
+        <v>7.066881937070973</v>
       </c>
       <c r="D15" t="n">
-        <v>47.83756346089351</v>
+        <v>7.773604062395195</v>
       </c>
       <c r="E15" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F15" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>62.53392050869</v>
+        <v>10.16176208266213</v>
       </c>
       <c r="D16" t="n">
-        <v>86.36369052241366</v>
+        <v>14.03409970989222</v>
       </c>
       <c r="E16" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F16" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>67.59951511989155</v>
+        <v>10.98492120698238</v>
       </c>
       <c r="D17" t="n">
-        <v>92.15757358442679</v>
+        <v>14.97560570746935</v>
       </c>
       <c r="E17" t="n">
-        <v>17.42933705550574</v>
+        <v>2.832267271519683</v>
       </c>
       <c r="F17" t="n">
-        <v>21.9634005440253</v>
+        <v>3.569052588404112</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
